--- a/top_by_archetype_book.xlsx
+++ b/top_by_archetype_book.xlsx
@@ -37,8 +37,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QARP" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reinvestment Inflection" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Owner-Operator" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Double Inflection" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiet Compounder" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global Geographic Footprint" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Double Inflection" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concentrated Segments" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiet Compounder" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diversified Segments" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fastest Segment Inflection" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H47"/>
+  <dimension ref="A3:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -649,17 +653,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>5,135</t>
+          <t>5,154</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1525,55 +1529,163 @@
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Double Inflection</t>
+          <t>Global Geographic Footprint</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>2</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>ACTG</t>
         </is>
       </c>
       <c r="H46" s="14" t="n">
-        <v>0.715784</v>
+        <v>0.5964970000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
+          <t>Double Inflection</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>KROS</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.715784</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated Segments</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>ACFN</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.292591</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
           <t>Quiet Compounder</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
+      <c r="C49" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>TBTC</t>
         </is>
       </c>
-      <c r="H47" s="14" t="n">
+      <c r="H49" s="14" t="n">
         <v>0.321513</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Diversified Segments</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>ACTG</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0.5964970000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Fastest Segment Inflection</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>AAME</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0.6477579999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1615,6 +1727,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26897,12 +27013,12 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Encore Capital Group, Inc.</t>
+          <t>Abercrombie &amp; Fitch Co. Class A</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
@@ -26912,16 +27028,16 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1749966464</v>
+        <v>3470864896</v>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
@@ -26929,37 +27045,37 @@
         </is>
       </c>
       <c r="I17" s="21" t="n">
-        <v>0.174253</v>
+        <v>0.18763</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>0.3007101895394635</v>
+        <v>0.234156702210471</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>2.438589495276524</v>
+        <v>4.058217123091529</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>6.56845005630208</v>
+        <v>9.55245355967282</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>1.691102565886619</v>
+        <v>2.472310889347138</v>
       </c>
       <c r="N17" s="22" t="n">
-        <v>10.90958049353796</v>
+        <v>-1.80577469529946</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>70.12189016130613</v>
+        <v>73.99485261591667</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>-0.1892679249589671</v>
+        <v>0.4367262300607629</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>68.05075124389802</v>
+        <v>16.67526221485629</v>
       </c>
       <c r="R17" s="22" t="n">
-        <v>99.70639804178246</v>
+        <v>0.65138090943851</v>
       </c>
       <c r="S17" s="16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
@@ -26968,12 +27084,12 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, Inc.</t>
+          <t>Encore Capital Group, Inc.</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -26983,16 +27099,16 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G18" s="12" t="n">
-        <v>8154581504</v>
+        <v>1749966464</v>
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
@@ -27000,34 +27116,34 @@
         </is>
       </c>
       <c r="I18" s="21" t="n">
-        <v>0.147834</v>
+        <v>0.174253</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>0.1959621294503184</v>
+        <v>0.3007101895394635</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>8.546565816176752</v>
+        <v>2.438589495276524</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>13.64625926713066</v>
+        <v>6.56845005630208</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>5.685646407853636</v>
+        <v>1.691102565886619</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>8.27726106690956</v>
+        <v>10.90958049353796</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>59.20094734536428</v>
+        <v>70.12189016130613</v>
       </c>
       <c r="P18" s="14" t="n">
-        <v>-0.1270076284563119</v>
+        <v>-0.1892679249589671</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>10.46178847349851</v>
+        <v>68.05075124389802</v>
       </c>
       <c r="R18" s="22" t="n">
-        <v>-46.39921073474694</v>
+        <v>99.70639804178246</v>
       </c>
       <c r="S18" s="16" t="n">
         <v>12</v>
@@ -27039,12 +27155,12 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Ubiquiti Inc.</t>
+          <t>Sprouts Farmers Market, Inc.</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
@@ -27054,16 +27170,16 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="G19" s="12" t="n">
-        <v>36967493632</v>
+        <v>8154581504</v>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
@@ -27071,37 +27187,37 @@
         </is>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0.310487</v>
+        <v>0.147834</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>0.4529706864500567</v>
+        <v>0.1959621294503184</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>33.54856205731382</v>
+        <v>8.546565816176752</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>40.66786243495671</v>
+        <v>13.64625926713066</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>30.74997224412658</v>
+        <v>5.685646407853636</v>
       </c>
       <c r="N19" s="22" t="n">
-        <v>1.41296027585665</v>
+        <v>8.27726106690956</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>121.7092792819379</v>
+        <v>59.20094734536428</v>
       </c>
       <c r="P19" s="14" t="n">
-        <v>-0.2681564891160144</v>
+        <v>-0.1270076284563119</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>36.34923357335341</v>
+        <v>10.46178847349851</v>
       </c>
       <c r="R19" s="22" t="n">
-        <v>56.54617669135972</v>
+        <v>-46.39921073474694</v>
       </c>
       <c r="S19" s="16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
@@ -27110,12 +27226,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch Co. Class A</t>
+          <t>Ubiquiti Inc.</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
@@ -27125,16 +27241,16 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3470864896</v>
+        <v>36967493632</v>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
@@ -27142,34 +27258,34 @@
         </is>
       </c>
       <c r="I20" s="21" t="n">
-        <v>0.18763</v>
+        <v>0.310487</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>0.234156702210471</v>
+        <v>0.4529706864500567</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>4.058217123091529</v>
+        <v>33.54856205731382</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>9.55245355967282</v>
+        <v>40.66786243495671</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>2.472310889347138</v>
+        <v>30.74997224412658</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>-1.80577469529946</v>
+        <v>1.41296027585665</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>73.99485261591667</v>
+        <v>121.7092792819379</v>
       </c>
       <c r="P20" s="14" t="n">
-        <v>0.4367262300607629</v>
+        <v>-0.2681564891160144</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>16.67526221485629</v>
+        <v>36.34923357335341</v>
       </c>
       <c r="R20" s="22" t="n">
-        <v>0.65138090943851</v>
+        <v>56.54617669135972</v>
       </c>
       <c r="S20" s="16" t="n">
         <v>11</v>
@@ -27181,12 +27297,12 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
@@ -27196,7 +27312,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -27205,7 +27321,7 @@
         </is>
       </c>
       <c r="G21" s="12" t="n">
-        <v>85881602048</v>
+        <v>98931990528</v>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
@@ -27213,37 +27329,37 @@
         </is>
       </c>
       <c r="I21" s="21" t="n">
-        <v>0.171423</v>
+        <v>0.218527</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>0.228564436766841</v>
+        <v>0.2913698523763092</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>18.61811017066556</v>
+        <v>10.21890603178509</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>20.30297920756501</v>
+        <v>14.0050949218573</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.320507347974018</v>
+        <v>8.65319605772763</v>
       </c>
       <c r="N21" s="22" t="n">
-        <v>0.6858279141914501</v>
+        <v>8.193507435500159</v>
       </c>
       <c r="O21" s="22" t="n">
-        <v>13.30983264314316</v>
+        <v>72.95730960737899</v>
       </c>
       <c r="P21" s="14" t="n">
-        <v>1.720735481521937</v>
+        <v>-0.0233696194946569</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>26.64564637399951</v>
+        <v>40.94794094794095</v>
       </c>
       <c r="R21" s="22" t="n">
-        <v>-44.70813513942883</v>
+        <v>-40.92631418456457</v>
       </c>
       <c r="S21" s="16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -27252,12 +27368,12 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated Class A</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
@@ -27267,16 +27383,16 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G22" s="12" t="n">
-        <v>440501895168</v>
+        <v>85881602048</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -27284,34 +27400,34 @@
         </is>
       </c>
       <c r="I22" s="21" t="n">
-        <v>0.162338</v>
+        <v>0.171423</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>0.2164506283292373</v>
+        <v>0.228564436766841</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>22.53385374359998</v>
+        <v>18.61811017066556</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>29.78376573144016</v>
+        <v>20.30297920756501</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>65.56063330376544</v>
+        <v>3.320507347974018</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>1.90464560811939</v>
+        <v>0.6858279141914501</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>106.3073200922748</v>
+        <v>13.30983264314316</v>
       </c>
       <c r="P22" s="14" t="n">
-        <v>0.5201637569996707</v>
+        <v>1.720735481521937</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>62.6152803559327</v>
+        <v>26.64564637399951</v>
       </c>
       <c r="R22" s="22" t="n">
-        <v>-12.04181397563146</v>
+        <v>-44.70813513942883</v>
       </c>
       <c r="S22" s="16" t="n">
         <v>11</v>
@@ -27323,12 +27439,12 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>USNA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>USANA Health Sciences, Inc.</t>
+          <t>Mastercard Incorporated Class A</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
@@ -27338,16 +27454,16 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
-        <v>331964960</v>
+        <v>440501895168</v>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
@@ -27355,37 +27471,37 @@
         </is>
       </c>
       <c r="I23" s="21" t="n">
-        <v>0.511209</v>
+        <v>0.162338</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>0.4809568687980463</v>
+        <v>0.2164506283292373</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>2.121406130508368</v>
+        <v>22.53385374359998</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>257.3371782945736</v>
+        <v>29.78376573144016</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.6227020618866113</v>
+        <v>65.56063330376544</v>
       </c>
       <c r="N23" s="22" t="n">
-        <v>13.55594879652358</v>
+        <v>1.90464560811939</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>12.47035837804196</v>
+        <v>106.3073200922748</v>
       </c>
       <c r="P23" s="14" t="n">
-        <v>-1.690365659002571</v>
+        <v>0.5201637569996707</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>8.870076097776069</v>
+        <v>62.6152803559327</v>
       </c>
       <c r="R23" s="22" t="n">
-        <v>-40.08663976972499</v>
+        <v>-12.04181397563146</v>
       </c>
       <c r="S23" s="16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -27394,12 +27510,12 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>USNA</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>USANA Health Sciences, Inc.</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -27409,7 +27525,7 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
@@ -27418,7 +27534,7 @@
         </is>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1027733376</v>
+        <v>331964960</v>
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
@@ -27426,34 +27542,34 @@
         </is>
       </c>
       <c r="I24" s="21" t="n">
-        <v>0.334306</v>
+        <v>0.511209</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>0.4125563397707107</v>
+        <v>0.4809568687980463</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>17.9170334911752</v>
+        <v>2.121406130508368</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>34.36086178535607</v>
+        <v>257.3371782945736</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>4.774292849710124</v>
+        <v>0.6227020618866113</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>-3.81694327693022</v>
+        <v>13.55594879652358</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>134.5739910313901</v>
+        <v>12.47035837804196</v>
       </c>
       <c r="P24" s="14" t="n">
-        <v>-3.510935474428136</v>
+        <v>-1.690365659002571</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>10.05683861240608</v>
+        <v>8.870076097776069</v>
       </c>
       <c r="R24" s="22" t="n">
-        <v>33.65774245100643</v>
+        <v>-40.08663976972499</v>
       </c>
       <c r="S24" s="16" t="n">
         <v>10</v>
@@ -27465,12 +27581,12 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>RPC, Inc.</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
@@ -27480,7 +27596,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
@@ -27489,7 +27605,7 @@
         </is>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1533734528</v>
+        <v>1027733376</v>
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
@@ -27497,34 +27613,34 @@
         </is>
       </c>
       <c r="I25" s="21" t="n">
-        <v>0.314555</v>
+        <v>0.334306</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>0.4012332699627008</v>
+        <v>0.4125563397707107</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>6.16378374579218</v>
+        <v>17.9170334911752</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>57.18835631455312</v>
+        <v>34.36086178535607</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.395355707164763</v>
+        <v>4.774292849710124</v>
       </c>
       <c r="N25" s="22" t="n">
-        <v>5.0639141638989</v>
+        <v>-3.81694327693022</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>5.7328723988691</v>
+        <v>134.5739910313901</v>
       </c>
       <c r="P25" s="14" t="n">
-        <v>-0.6005680093852906</v>
+        <v>-3.510935474428136</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>13.57282766269552</v>
+        <v>10.05683861240608</v>
       </c>
       <c r="R25" s="22" t="n">
-        <v>47.18247379226999</v>
+        <v>33.65774245100643</v>
       </c>
       <c r="S25" s="16" t="n">
         <v>10</v>
@@ -27536,12 +27652,12 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>Tandy Leather Factory Inc. Common Stock</t>
+          <t>RPC, Inc.</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
@@ -27551,16 +27667,16 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G26" s="12" t="n">
-        <v>19137386</v>
+        <v>1533734528</v>
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
@@ -27568,36 +27684,34 @@
         </is>
       </c>
       <c r="I26" s="21" t="n">
-        <v>0.300119</v>
+        <v>0.314555</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>0.2873325199547349</v>
+        <v>0.4012332699627008</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>9.873645901639344</v>
-      </c>
-      <c r="L26" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.16378374579218</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>57.18835631455312</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>0.3638908938791808</v>
+        <v>1.395355707164763</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>-5.115641185269499</v>
+        <v>5.0639141638989</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>0.04120992334954</v>
+        <v>5.7328723988691</v>
       </c>
       <c r="P26" s="14" t="n">
-        <v>2.172566371681416</v>
+        <v>-0.6005680093852906</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>6.81035047494268</v>
+        <v>13.57282766269552</v>
       </c>
       <c r="R26" s="22" t="n">
-        <v>7.97562155237055</v>
+        <v>47.18247379226999</v>
       </c>
       <c r="S26" s="16" t="n">
         <v>10</v>
@@ -27609,12 +27723,12 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>TLF</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Tandy Leather Factory Inc. Common Stock</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
@@ -27624,16 +27738,16 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>19410835456</v>
+        <v>19137386</v>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
@@ -27641,34 +27755,36 @@
         </is>
       </c>
       <c r="I27" s="21" t="n">
-        <v>0.274114</v>
+        <v>0.300119</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0.3752775108643964</v>
+        <v>0.2873325199547349</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>22.79695698269598</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <v>12.6249582639836</v>
+        <v>9.873645901639344</v>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M27" s="14" t="n">
-        <v>3.452136516608045</v>
+        <v>0.3638908938791808</v>
       </c>
       <c r="N27" s="22" t="n">
-        <v>3.22502862599094</v>
+        <v>-5.115641185269499</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>6.744712005563399</v>
+        <v>0.04120992334954</v>
       </c>
       <c r="P27" s="14" t="n">
-        <v>-2.125364258516113</v>
+        <v>2.172566371681416</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>34.89865734505747</v>
+        <v>6.81035047494268</v>
       </c>
       <c r="R27" s="22" t="n">
-        <v>50.61230885860076</v>
+        <v>7.97562155237055</v>
       </c>
       <c r="S27" s="16" t="n">
         <v>10</v>
@@ -27680,12 +27796,12 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>Iradimed Corporation</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -27700,11 +27816,11 @@
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1104965632</v>
+        <v>19410835456</v>
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
@@ -27712,36 +27828,34 @@
         </is>
       </c>
       <c r="I28" s="21" t="n">
-        <v>0.260127</v>
+        <v>0.274114</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0.3794676991122523</v>
+        <v>0.3752775108643964</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>38.2304418611731</v>
+        <v>22.79695698269598</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>48.16223462981965</v>
+        <v>12.6249582639836</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>11.21633099863979</v>
+        <v>3.452136516608045</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>1.14838060411276</v>
+        <v>3.22502862599094</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>62.38776222116754</v>
-      </c>
-      <c r="P28" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.744712005563399</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>-2.125364258516113</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>33.00580217342728</v>
+        <v>34.89865734505747</v>
       </c>
       <c r="R28" s="22" t="n">
-        <v>63.23947071163466</v>
+        <v>50.61230885860076</v>
       </c>
       <c r="S28" s="16" t="n">
         <v>10</v>
@@ -27753,12 +27867,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>RCM Technologies, Inc.</t>
+          <t>Iradimed Corporation</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
@@ -27768,16 +27882,16 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
-        <v>163865648</v>
+        <v>1104965632</v>
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
@@ -27785,34 +27899,36 @@
         </is>
       </c>
       <c r="I29" s="21" t="n">
-        <v>0.259844</v>
+        <v>0.260127</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0.3384714053740679</v>
+        <v>0.3794676991122523</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>6.531825650166086</v>
+        <v>38.2304418611731</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>11.98461551963724</v>
+        <v>48.16223462981965</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>3.564311306390568</v>
+        <v>11.21633099863979</v>
       </c>
       <c r="N29" s="22" t="n">
-        <v>14.27938087426353</v>
+        <v>1.14838060411276</v>
       </c>
       <c r="O29" s="22" t="n">
-        <v>55.34887070062165</v>
-      </c>
-      <c r="P29" s="14" t="n">
-        <v>0.8158970704077422</v>
+        <v>62.38776222116754</v>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>8.34648282426018</v>
+        <v>33.00580217342728</v>
       </c>
       <c r="R29" s="22" t="n">
-        <v>-0.77252533785857</v>
+        <v>63.23947071163466</v>
       </c>
       <c r="S29" s="16" t="n">
         <v>10</v>
@@ -27824,12 +27940,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>Karat Packaging Inc.</t>
+          <t>RCM Technologies, Inc.</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
@@ -27839,16 +27955,16 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="G30" s="12" t="n">
-        <v>534429120</v>
+        <v>163865648</v>
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
@@ -27856,34 +27972,34 @@
         </is>
       </c>
       <c r="I30" s="21" t="n">
-        <v>0.254432</v>
+        <v>0.259844</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>0.3298318836949814</v>
+        <v>0.3384714053740679</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>9.942301882452172</v>
+        <v>6.531825650166086</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>18.55012565081569</v>
+        <v>11.98461551963724</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>3.501170181403668</v>
+        <v>3.564311306390568</v>
       </c>
       <c r="N30" s="22" t="n">
-        <v>6.3215118218109</v>
+        <v>14.27938087426353</v>
       </c>
       <c r="O30" s="22" t="n">
-        <v>31.448035969256</v>
+        <v>55.34887070062165</v>
       </c>
       <c r="P30" s="14" t="n">
-        <v>0.0997593241693453</v>
+        <v>0.8158970704077422</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>13.23568711878104</v>
+        <v>8.34648282426018</v>
       </c>
       <c r="R30" s="22" t="n">
-        <v>-5.77542186327034</v>
+        <v>-0.77252533785857</v>
       </c>
       <c r="S30" s="16" t="n">
         <v>10</v>
@@ -27895,12 +28011,12 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>LNN</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Lindsay Corporation</t>
+          <t>Karat Packaging Inc.</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -27910,7 +28026,7 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
@@ -27919,7 +28035,7 @@
         </is>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1101190400</v>
+        <v>534429120</v>
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
@@ -27927,34 +28043,34 @@
         </is>
       </c>
       <c r="I31" s="21" t="n">
-        <v>0.251719</v>
+        <v>0.254432</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>0.3146098280238565</v>
+        <v>0.3298318836949814</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>9.412008625888632</v>
+        <v>9.942301882452172</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>14.75236653493201</v>
+        <v>18.55012565081569</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>2.168709417582612</v>
+        <v>3.501170181403668</v>
       </c>
       <c r="N31" s="22" t="n">
-        <v>1.19897521809125</v>
+        <v>6.3215118218109</v>
       </c>
       <c r="O31" s="22" t="n">
-        <v>20.27833001988071</v>
+        <v>31.448035969256</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>-0.5052239995748525</v>
+        <v>0.0997593241693453</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>14.78031783535148</v>
+        <v>13.23568711878104</v>
       </c>
       <c r="R31" s="22" t="n">
-        <v>-24.4254979521366</v>
+        <v>-5.77542186327034</v>
       </c>
       <c r="S31" s="16" t="n">
         <v>10</v>
@@ -27966,12 +28082,12 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>LNN</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>Manhattan Associates, Inc.</t>
+          <t>Lindsay Corporation</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -27981,16 +28097,16 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G32" s="12" t="n">
-        <v>8202579968</v>
+        <v>1101190400</v>
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
@@ -27998,36 +28114,34 @@
         </is>
       </c>
       <c r="I32" s="21" t="n">
-        <v>0.2482</v>
+        <v>0.251719</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>0.3273111667878909</v>
+        <v>0.3146098280238565</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>28.052200926346</v>
+        <v>9.412008625888632</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>37.74945910074094</v>
+        <v>14.75236653493201</v>
       </c>
       <c r="M32" s="14" t="n">
-        <v>39.97845725843792</v>
+        <v>2.168709417582612</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>3.22798437848768</v>
-      </c>
-      <c r="O32" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.19897521809125</v>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>20.27833001988071</v>
       </c>
       <c r="P32" s="14" t="n">
-        <v>-0.5914595637479093</v>
+        <v>-0.5052239995748525</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>26.17884849475845</v>
+        <v>14.78031783535148</v>
       </c>
       <c r="R32" s="22" t="n">
-        <v>-26.05472541057486</v>
+        <v>-24.4254979521366</v>
       </c>
       <c r="S32" s="16" t="n">
         <v>10</v>
@@ -28039,12 +28153,12 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Napco Security Technologies, Inc.</t>
+          <t>Manhattan Associates, Inc.</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
@@ -28054,16 +28168,16 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1294044160</v>
+        <v>8202579968</v>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
@@ -28071,34 +28185,36 @@
         </is>
       </c>
       <c r="I33" s="21" t="n">
-        <v>0.225246</v>
+        <v>0.2482</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>0.285188525457007</v>
+        <v>0.3273111667878909</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>29.37261527770884</v>
+        <v>28.052200926346</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>33.38348837809251</v>
+        <v>37.74945910074094</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>7.278825527893712</v>
+        <v>39.97845725843792</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>2.42688781192753</v>
-      </c>
-      <c r="O33" s="22" t="n">
-        <v>57.00823448972918</v>
+        <v>3.22798437848768</v>
+      </c>
+      <c r="O33" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P33" s="14" t="n">
-        <v>-2.081081081081081</v>
+        <v>-0.5914595637479093</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>29.17137772459705</v>
+        <v>26.17884849475845</v>
       </c>
       <c r="R33" s="22" t="n">
-        <v>33.07762979470414</v>
+        <v>-26.05472541057486</v>
       </c>
       <c r="S33" s="16" t="n">
         <v>10</v>
@@ -28110,12 +28226,12 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>The Trade Desk, Inc.</t>
+          <t>Napco Security Technologies, Inc.</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -28125,16 +28241,16 @@
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="G34" s="12" t="n">
-        <v>10521024512</v>
+        <v>1294044160</v>
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
@@ -28142,34 +28258,34 @@
         </is>
       </c>
       <c r="I34" s="21" t="n">
-        <v>0.224652</v>
+        <v>0.225246</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>0.2790362501490468</v>
+        <v>0.285188525457007</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>19.45863252251052</v>
+        <v>29.37261527770884</v>
       </c>
       <c r="L34" s="14" t="n">
-        <v>31.33103588424131</v>
+        <v>33.38348837809251</v>
       </c>
       <c r="M34" s="14" t="n">
-        <v>4.28819423139158</v>
+        <v>7.278825527893712</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>8.25061284678052</v>
+        <v>2.42688781192753</v>
       </c>
       <c r="O34" s="22" t="n">
-        <v>25.33761155577169</v>
+        <v>57.00823448972918</v>
       </c>
       <c r="P34" s="14" t="n">
-        <v>-1.332112878510503</v>
+        <v>-2.081081081081081</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>24.83665193727434</v>
+        <v>29.17137772459705</v>
       </c>
       <c r="R34" s="22" t="n">
-        <v>-69.89102837420306</v>
+        <v>33.07762979470414</v>
       </c>
       <c r="S34" s="16" t="n">
         <v>10</v>
@@ -28181,12 +28297,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>WFCF</t>
+          <t>TTD</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Where Food Comes From, Inc.</t>
+          <t>The Trade Desk, Inc.</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
@@ -28196,16 +28312,16 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G35" s="12" t="n">
-        <v>46512516</v>
+        <v>10521024512</v>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
@@ -28213,34 +28329,34 @@
         </is>
       </c>
       <c r="I35" s="21" t="n">
-        <v>0.208229</v>
+        <v>0.224652</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>0.2681640704653441</v>
+        <v>0.2790362501490468</v>
       </c>
       <c r="K35" s="14" t="n">
-        <v>20.13029376989541</v>
+        <v>19.45863252251052</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>19.6920050804403</v>
+        <v>31.33103588424131</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>4.998658355722729</v>
+        <v>4.28819423139158</v>
       </c>
       <c r="N35" s="22" t="n">
-        <v>4.55791297120972</v>
+        <v>8.25061284678052</v>
       </c>
       <c r="O35" s="22" t="n">
-        <v>22.49065286166235</v>
+        <v>25.33761155577169</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.7831367106176267</v>
+        <v>-1.332112878510503</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>11.57801703358508</v>
+        <v>24.83665193727434</v>
       </c>
       <c r="R35" s="22" t="n">
-        <v>-5.81633303474245</v>
+        <v>-69.89102837420306</v>
       </c>
       <c r="S35" s="16" t="n">
         <v>10</v>
@@ -28252,12 +28368,12 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>WFCF</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>Morningstar, Inc.</t>
+          <t>Where Food Comes From, Inc.</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
@@ -28267,16 +28383,16 @@
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6831352832</v>
+        <v>46512516</v>
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
@@ -28284,34 +28400,34 @@
         </is>
       </c>
       <c r="I36" s="21" t="n">
-        <v>0.203137</v>
+        <v>0.208229</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>0.2708499929346525</v>
+        <v>0.2681640704653441</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>11.76148204634893</v>
+        <v>20.13029376989541</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>18.13473010883992</v>
+        <v>19.6920050804403</v>
       </c>
       <c r="M36" s="14" t="n">
-        <v>6.705951538235006</v>
+        <v>4.998658355722729</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>2.42704489253352</v>
+        <v>4.55791297120972</v>
       </c>
       <c r="O36" s="22" t="n">
-        <v>23.16894855775621</v>
+        <v>22.49065286166235</v>
       </c>
       <c r="P36" s="14" t="n">
-        <v>1.577654209233157</v>
+        <v>-0.7831367106176267</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>30.82841652049115</v>
+        <v>11.57801703358508</v>
       </c>
       <c r="R36" s="22" t="n">
-        <v>-40.9052016570997</v>
+        <v>-5.81633303474245</v>
       </c>
       <c r="S36" s="16" t="n">
         <v>10</v>
@@ -28323,12 +28439,12 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>Morningstar, Inc.</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
@@ -28338,16 +28454,16 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="G37" s="12" t="n">
-        <v>8012766208</v>
+        <v>6831352832</v>
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
@@ -28355,34 +28471,34 @@
         </is>
       </c>
       <c r="I37" s="21" t="n">
-        <v>0.192629</v>
+        <v>0.203137</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>0.2586486199492636</v>
+        <v>0.2708499929346525</v>
       </c>
       <c r="K37" s="14" t="n">
-        <v>8.342641077091852</v>
+        <v>11.76148204634893</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>14.40367824555096</v>
+        <v>18.13473010883992</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>1.794050155161991</v>
+        <v>6.705951538235006</v>
       </c>
       <c r="N37" s="22" t="n">
-        <v>-12.26542712576295</v>
+        <v>2.42704489253352</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>16.79913669661942</v>
+        <v>23.16894855775621</v>
       </c>
       <c r="P37" s="14" t="n">
-        <v>0.8170053768340472</v>
+        <v>1.577654209233157</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>10.52333777679744</v>
+        <v>30.82841652049115</v>
       </c>
       <c r="R37" s="22" t="n">
-        <v>32.01465981191977</v>
+        <v>-40.9052016570997</v>
       </c>
       <c r="S37" s="16" t="n">
         <v>10</v>
@@ -28394,12 +28510,12 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>MHO</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>M/I Homes, Inc.</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -28414,11 +28530,11 @@
       </c>
       <c r="F38" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3345164288</v>
+        <v>8012766208</v>
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
@@ -28426,36 +28542,34 @@
         </is>
       </c>
       <c r="I38" s="21" t="n">
-        <v>0.181132</v>
+        <v>0.192629</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>0.2212160245526014</v>
+        <v>0.2586486199492636</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>4.843015528096179</v>
+        <v>8.342641077091852</v>
       </c>
       <c r="L38" s="14" t="n">
-        <v>8.223077290672121</v>
+        <v>14.40367824555096</v>
       </c>
       <c r="M38" s="14" t="n">
-        <v>1.047874810013495</v>
+        <v>1.794050155161991</v>
       </c>
       <c r="N38" s="22" t="n">
-        <v>16.86138411866245</v>
+        <v>-12.26542712576295</v>
       </c>
       <c r="O38" s="22" t="n">
-        <v>21.36061620278805</v>
-      </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.79913669661942</v>
+      </c>
+      <c r="P38" s="14" t="n">
+        <v>0.8170053768340472</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>12.69954091720643</v>
+        <v>10.52333777679744</v>
       </c>
       <c r="R38" s="22" t="n">
-        <v>22.12606170952692</v>
+        <v>32.01465981191977</v>
       </c>
       <c r="S38" s="16" t="n">
         <v>10</v>
@@ -28467,12 +28581,12 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>MHO</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>EMCOR Group, Inc.</t>
+          <t>M/I Homes, Inc.</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
@@ -28487,11 +28601,11 @@
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="G39" s="12" t="n">
-        <v>37804142592</v>
+        <v>3345164288</v>
       </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
@@ -28499,34 +28613,36 @@
         </is>
       </c>
       <c r="I39" s="21" t="n">
-        <v>0.17835</v>
+        <v>0.181132</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>0.2931262524258592</v>
+        <v>0.2212160245526014</v>
       </c>
       <c r="K39" s="14" t="n">
-        <v>22.8931864156639</v>
+        <v>4.843015528096179</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>33.05442066846552</v>
+        <v>8.223077290672121</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>9.777256246995051</v>
+        <v>1.047874810013495</v>
       </c>
       <c r="N39" s="22" t="n">
-        <v>0.12476674979524</v>
+        <v>16.86138411866245</v>
       </c>
       <c r="O39" s="22" t="n">
-        <v>52.32022843824266</v>
-      </c>
-      <c r="P39" s="14" t="n">
-        <v>-0.2014116605863134</v>
+        <v>21.36061620278805</v>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>11.35825692304562</v>
+        <v>12.69954091720643</v>
       </c>
       <c r="R39" s="22" t="n">
-        <v>85.58112867578578</v>
+        <v>22.12606170952692</v>
       </c>
       <c r="S39" s="16" t="n">
         <v>10</v>
@@ -28538,12 +28654,12 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>EMCOR Group, Inc.</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -28553,7 +28669,7 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
@@ -28562,7 +28678,7 @@
         </is>
       </c>
       <c r="G40" s="12" t="n">
-        <v>44124782592</v>
+        <v>37804142592</v>
       </c>
       <c r="H40" s="20" t="inlineStr">
         <is>
@@ -28570,34 +28686,34 @@
         </is>
       </c>
       <c r="I40" s="21" t="n">
-        <v>0.172264</v>
+        <v>0.17835</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>0.2296849346582146</v>
+        <v>0.2931262524258592</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>28.87072718743677</v>
+        <v>22.8931864156639</v>
       </c>
       <c r="L40" s="14" t="n">
-        <v>38.67087448051504</v>
+        <v>33.05442066846552</v>
       </c>
       <c r="M40" s="14" t="n">
-        <v>28.35595239646733</v>
+        <v>9.777256246995051</v>
       </c>
       <c r="N40" s="22" t="n">
-        <v>1.71085942106572</v>
+        <v>0.12476674979524</v>
       </c>
       <c r="O40" s="22" t="n">
-        <v>77.93241041172554</v>
+        <v>52.32022843824266</v>
       </c>
       <c r="P40" s="14" t="n">
-        <v>0.5004395492902034</v>
+        <v>-0.2014116605863134</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>35.02572482144443</v>
+        <v>11.35825692304562</v>
       </c>
       <c r="R40" s="22" t="n">
-        <v>10.80363884785092</v>
+        <v>85.58112867578578</v>
       </c>
       <c r="S40" s="16" t="n">
         <v>10</v>
@@ -28609,12 +28725,12 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
@@ -28624,7 +28740,7 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
@@ -28633,7 +28749,7 @@
         </is>
       </c>
       <c r="G41" s="12" t="n">
-        <v>34754215936</v>
+        <v>44124782592</v>
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
@@ -28641,34 +28757,34 @@
         </is>
       </c>
       <c r="I41" s="21" t="n">
-        <v>0.159163</v>
+        <v>0.172264</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>0.212216880293301</v>
+        <v>0.2296849346582146</v>
       </c>
       <c r="K41" s="14" t="n">
-        <v>13.49943675721804</v>
+        <v>28.87072718743677</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>18.69712499246826</v>
+        <v>38.67087448051504</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>8.659112999800678</v>
+        <v>28.35595239646733</v>
       </c>
       <c r="N41" s="22" t="n">
-        <v>7.05669782485177</v>
+        <v>1.71085942106572</v>
       </c>
       <c r="O41" s="22" t="n">
-        <v>35.95194596689365</v>
+        <v>77.93241041172554</v>
       </c>
       <c r="P41" s="14" t="n">
-        <v>1.135001413627368</v>
+        <v>0.5004395492902034</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>44.67460292399507</v>
+        <v>35.02572482144443</v>
       </c>
       <c r="R41" s="22" t="n">
-        <v>-35.33806931458471</v>
+        <v>10.80363884785092</v>
       </c>
       <c r="S41" s="16" t="n">
         <v>10</v>
@@ -28680,12 +28796,12 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>PSN</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Parsons Corporation</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
@@ -28700,11 +28816,11 @@
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="G42" s="12" t="n">
-        <v>5745816064</v>
+        <v>34754215936</v>
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
@@ -28712,34 +28828,34 @@
         </is>
       </c>
       <c r="I42" s="21" t="n">
-        <v>0.155468</v>
+        <v>0.159163</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>0.2072905212239557</v>
+        <v>0.212216880293301</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>14.11911802072073</v>
+        <v>13.49943675721804</v>
       </c>
       <c r="L42" s="14" t="n">
-        <v>21.76000387799465</v>
+        <v>18.69712499246826</v>
       </c>
       <c r="M42" s="14" t="n">
-        <v>2.168549166991557</v>
+        <v>8.659112999800678</v>
       </c>
       <c r="N42" s="22" t="n">
-        <v>-2.32992143341955</v>
+        <v>7.05669782485177</v>
       </c>
       <c r="O42" s="22" t="n">
-        <v>10.53270847078581</v>
+        <v>35.95194596689365</v>
       </c>
       <c r="P42" s="14" t="n">
-        <v>2.262897503079492</v>
+        <v>1.135001413627368</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>8.61932617379834</v>
+        <v>44.67460292399507</v>
       </c>
       <c r="R42" s="22" t="n">
-        <v>-20.91003359135387</v>
+        <v>-35.33806931458471</v>
       </c>
       <c r="S42" s="16" t="n">
         <v>10</v>
@@ -58368,6 +58484,2468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:S42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Global Geographic Footprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MATCHES</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>TOP SCORER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>ACTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>0.1% of universe</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>high conviction</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>risk-flagged</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>no thesis</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>by entry today asymmetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TOP NAMES MATCHING GLOBAL GEOGRAPHIC FOOTPRINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Mcap (USD)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>FCF yld %</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>ROIC %</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA m %</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Mom 12m %</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>Arch #</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>ACTG</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Acacia Research Corporation</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>442378240</v>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0.5964970000000001</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0.6554225327075763</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>5.916304114396459</v>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.8140182905511086</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>12.17080659301868</v>
+      </c>
+      <c r="O13" s="22" t="n">
+        <v>3.56924240530466</v>
+      </c>
+      <c r="P13" s="14" t="n">
+        <v>-3.064616009946442</v>
+      </c>
+      <c r="Q13" s="22" t="n">
+        <v>29.32630279912492</v>
+      </c>
+      <c r="R13" s="22" t="n">
+        <v>23.45013144510961</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>AOUT</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>American Outdoor Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>109709072</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.344308</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0.3352564159911202</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>16.16439973958333</v>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>0.6622184717720273</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>2.06181672924915</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>-5.36986230792019</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>6.624518803671898</v>
+      </c>
+      <c r="Q14" s="22" t="n">
+        <v>1.64395698547846</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <v>-31.47128236030416</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>ACNT</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Ascent Industries Co. Common Stock</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>125631184</v>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0.340007</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>0.3582419392309881</v>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>1.444169394886886</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>4.90164925931128</v>
+      </c>
+      <c r="O15" s="22" t="n">
+        <v>-20.42578356002365</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>23.70254191454841</v>
+      </c>
+      <c r="Q15" s="22" t="n">
+        <v>-2.25928641251221</v>
+      </c>
+      <c r="R15" s="22" t="n">
+        <v>16.02671243454434</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>C3.ai, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1256769024</v>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.285506</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0.3348649814764858</v>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>1.746791087365335</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>-15.28809163265946</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>-84.84292507582282</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>1.361942482753441</v>
+      </c>
+      <c r="Q16" s="22" t="n">
+        <v>-147.2713905091561</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>-63.04998003027967</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>ALGM</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Allegro MicroSystems, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>8556919296</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0.273882</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0.3989598357399593</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>100.7834839219331</v>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>8.962499275724355</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>1.45955566109384</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>1.72249294213012</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>1.583960335173133</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>8.40662130826337</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>77.3446585625084</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>AIOT</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>PowerFleet Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>433295712</v>
+      </c>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0.244271</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.3725892090167739</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>7.923658986175115</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0.8933398044240654</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>2.04086949284187</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>2.9003629898511</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>2.789020025371511</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>20.39337067621412</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>-44.97444493960414</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>ARAY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Accuray Incorporated</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>32120200</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0.234363</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0.2944255689382078</v>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0.7701393051526123</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>-28.16607617636253</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>-20.7761053621825</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>-13.87114737114737</v>
+      </c>
+      <c r="Q19" s="22" t="n">
+        <v>-1.8018018018018</v>
+      </c>
+      <c r="R19" s="22" t="n">
+        <v>-83.01886760624078</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>ALOT</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Astronova, Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>109546040</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0.233399</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.3433345477031998</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>25.10553464156988</v>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>1.413096153350017</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>14.9033228403327</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>2.90510213919209</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>3.170004004805767</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>3.27812895899384</v>
+      </c>
+      <c r="R20" s="22" t="n">
+        <v>63.49023775834199</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>AIRG</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Airgain, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>86702336</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0.227457</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0.3365420639713895</v>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>3.064878079819011</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>-5.28590140870022</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>-39.14209115281501</v>
+      </c>
+      <c r="P21" s="14" t="n">
+        <v>0.5552769070010449</v>
+      </c>
+      <c r="Q21" s="22" t="n">
+        <v>-9.24119816914193</v>
+      </c>
+      <c r="R21" s="22" t="n">
+        <v>71.85929949267162</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>ADTN</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Adtran Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1207681536</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.227026</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.3671204310526602</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>33.56439486457765</v>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>8.781541799672787</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>7.33521192129909</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>-13.91397084962673</v>
+      </c>
+      <c r="P22" s="14" t="n">
+        <v>-1.122152971249677</v>
+      </c>
+      <c r="Q22" s="22" t="n">
+        <v>3.22877997798453</v>
+      </c>
+      <c r="R22" s="22" t="n">
+        <v>82.05128951562541</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>AMCX</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Amc Global Media Inc.</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>364600032</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.2596434397260048</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>5.110140868666113</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>3.023819267515924</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0.3816850167183466</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>43.64563522583564</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>10.00957540667602</v>
+      </c>
+      <c r="P23" s="14" t="n">
+        <v>3.917148204621456</v>
+      </c>
+      <c r="Q23" s="22" t="n">
+        <v>13.52815802578432</v>
+      </c>
+      <c r="R23" s="22" t="n">
+        <v>29.28349053114311</v>
+      </c>
+      <c r="S23" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>AOSL</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Alpha and Omega Semiconductor Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>1163362688</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0.225155</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.3050382935032772</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>86.23534962505514</v>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>1.453874420912269</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>0.19349081960586</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>-6.9779064164507</v>
+      </c>
+      <c r="P24" s="14" t="n">
+        <v>-7.73156101540381</v>
+      </c>
+      <c r="Q24" s="22" t="n">
+        <v>3.04201214527618</v>
+      </c>
+      <c r="R24" s="22" t="n">
+        <v>65.68627642279596</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Adobe Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>98931990528</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0.218527</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.2913698523763092</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>10.21890603178509</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>14.0050949218573</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>8.65319605772763</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>8.193507435500159</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>72.95730960737899</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>-0.0233696194946569</v>
+      </c>
+      <c r="Q25" s="22" t="n">
+        <v>40.94794094794095</v>
+      </c>
+      <c r="R25" s="22" t="n">
+        <v>-40.92631418456457</v>
+      </c>
+      <c r="S25" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>ADUS</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Addus HomeCare Corporation</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>1698121344</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>0.21512</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.2861016948942989</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>11.50141334932926</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>18.62036409092404</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>1.564651847456425</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>7.247420829780229</v>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>11.79815839803427</v>
+      </c>
+      <c r="P26" s="14" t="n">
+        <v>0.2498396509789228</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>11.06964352245646</v>
+      </c>
+      <c r="R26" s="22" t="n">
+        <v>-17.21564868631061</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>AMBA</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Ambarella, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>3840072960</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0.198143</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>0.2654922317911493</v>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>6.456193641778849</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>-0.40892452210074</v>
+      </c>
+      <c r="O27" s="22" t="n">
+        <v>-16.99537013482574</v>
+      </c>
+      <c r="P27" s="14" t="n">
+        <v>5.253991393694564</v>
+      </c>
+      <c r="Q27" s="22" t="n">
+        <v>-14.57248747126966</v>
+      </c>
+      <c r="R27" s="22" t="n">
+        <v>38.66012654113409</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Acco Brands Corporation</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>347048000</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>0.191779</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0.2261550013098901</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>16.37218424962853</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>4.242640586797066</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>0.5102146427521317</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>-1.06613494386943</v>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>2.9198606271777</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>11.21545319465082</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>4.67490969713809</v>
+      </c>
+      <c r="R28" s="22" t="n">
+        <v>5.32423370937436</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>ANF</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch Co. Class A</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>3470864896</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>0.18763</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>0.234156702210471</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>4.058217123091529</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>9.55245355967282</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>2.472310889347138</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>-1.80577469529946</v>
+      </c>
+      <c r="O29" s="22" t="n">
+        <v>73.99485261591667</v>
+      </c>
+      <c r="P29" s="14" t="n">
+        <v>0.4367262300607629</v>
+      </c>
+      <c r="Q29" s="22" t="n">
+        <v>16.67526221485629</v>
+      </c>
+      <c r="R29" s="22" t="n">
+        <v>0.65138090943851</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc. Class A</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>78550376448</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>0.185561</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>0.2383269147600118</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>31.11369909503785</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>27.87451257913414</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>10.28684867050812</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>8.88771679486681</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>76.80546519193233</v>
+      </c>
+      <c r="P30" s="14" t="n">
+        <v>-3.653935185185185</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>20.49497904641417</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>3.68194635444941</v>
+      </c>
+      <c r="S30" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Arista Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>193949859840</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>0.183709</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>0.2760262237369417</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>47.39669737181394</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>54.1986474332821</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>14.38039755321752</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>1.68141910630421</v>
+      </c>
+      <c r="O31" s="22" t="n">
+        <v>37.21395453185761</v>
+      </c>
+      <c r="P31" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>43.71132232927635</v>
+      </c>
+      <c r="R31" s="22" t="n">
+        <v>66.4109797342966</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Analog Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>193407647744</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>0.183277</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>0.3112991279776929</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>46.8849507718971</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>62.48098758182941</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>5.731950050075524</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>2.26621545276302</v>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>9.819221046127851</v>
+      </c>
+      <c r="P32" s="14" t="n">
+        <v>1.003346988184371</v>
+      </c>
+      <c r="Q32" s="22" t="n">
+        <v>48.87752485382285</v>
+      </c>
+      <c r="R32" s="22" t="n">
+        <v>90.21757087039752</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Autodesk, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>50883895296</v>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>0.179394</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>0.2388741361990217</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>26.91767266242038</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>34.85198307945205</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>16.71063884926108</v>
+      </c>
+      <c r="N33" s="22" t="n">
+        <v>5.1745252298068</v>
+      </c>
+      <c r="O33" s="22" t="n">
+        <v>55.93108018555335</v>
+      </c>
+      <c r="P33" s="14" t="n">
+        <v>0.1240063593004769</v>
+      </c>
+      <c r="Q33" s="22" t="n">
+        <v>26.1865112406328</v>
+      </c>
+      <c r="R33" s="22" t="n">
+        <v>-18.30847271418167</v>
+      </c>
+      <c r="S33" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Adeia Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2962490368</v>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>0.179266</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>0.3247577776702575</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>32.04735952459558</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>49.2623570846567</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>6.349549728120506</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>8.24856690301988</v>
+      </c>
+      <c r="O34" s="22" t="n">
+        <v>12.5643562633467</v>
+      </c>
+      <c r="P34" s="14" t="n">
+        <v>1.332183559148983</v>
+      </c>
+      <c r="Q34" s="22" t="n">
+        <v>55.08786331022741</v>
+      </c>
+      <c r="R34" s="22" t="n">
+        <v>109.352481287542</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Alamo Group Inc.</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>1825494912</v>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>0.177732</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>0.2216114202439745</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>9.130379717736808</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>15.53969773479864</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>1.556362485548936</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <v>-1.81583634016724</v>
+      </c>
+      <c r="O35" s="22" t="n">
+        <v>14.98577917020364</v>
+      </c>
+      <c r="P35" s="14" t="n">
+        <v>0.4545055385599267</v>
+      </c>
+      <c r="Q35" s="22" t="n">
+        <v>12.85534083393357</v>
+      </c>
+      <c r="R35" s="22" t="n">
+        <v>-23.99930768693225</v>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Agilent Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>32487960576</v>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>0.176896</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>0.2358608671721763</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>20.25950034285714</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>27.18657788786611</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>4.702947390851187</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>3.45974317892499</v>
+      </c>
+      <c r="O36" s="22" t="n">
+        <v>16.28604382929642</v>
+      </c>
+      <c r="P36" s="14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q36" s="22" t="n">
+        <v>25.81740976645435</v>
+      </c>
+      <c r="R36" s="22" t="n">
+        <v>5.67433603220212</v>
+      </c>
+      <c r="S36" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>AOS</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>A.O. Smith Corporation</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>7894823424</v>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="n">
+        <v>0.175297</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>0.2337295390474511</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>10.22653657290259</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>14.65260472160356</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>4.204070197561106</v>
+      </c>
+      <c r="N37" s="22" t="n">
+        <v>4.191354033252661</v>
+      </c>
+      <c r="O37" s="22" t="n">
+        <v>31.50963829326402</v>
+      </c>
+      <c r="P37" s="14" t="n">
+        <v>0.5418396879325532</v>
+      </c>
+      <c r="Q37" s="22" t="n">
+        <v>20.84787114037619</v>
+      </c>
+      <c r="R37" s="22" t="n">
+        <v>-13.18781776366073</v>
+      </c>
+      <c r="S37" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>AEIS</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Advanced Energy Industries, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>12997861376</v>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>0.174309</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>0.3665138252956994</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>54.71249012836385</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>79.54627525091799</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>9.388804807859</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>-0.35579699353765</v>
+      </c>
+      <c r="O38" s="22" t="n">
+        <v>9.86657881732828</v>
+      </c>
+      <c r="P38" s="14" t="n">
+        <v>-0.0577058409570724</v>
+      </c>
+      <c r="Q38" s="22" t="n">
+        <v>14.91706907411295</v>
+      </c>
+      <c r="R38" s="22" t="n">
+        <v>180.9349435765432</v>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>2864833626112</v>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="n">
+        <v>0.165905</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>0.2220950126226959</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>20.85235725415251</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>33.03049157889154</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>6.482785397412166</v>
+      </c>
+      <c r="N39" s="22" t="n">
+        <v>-0.8870672198332499</v>
+      </c>
+      <c r="O39" s="22" t="n">
+        <v>17.0669518012831</v>
+      </c>
+      <c r="P39" s="14" t="n">
+        <v>0.09158449994162531</v>
+      </c>
+      <c r="Q39" s="22" t="n">
+        <v>25.36942496795804</v>
+      </c>
+      <c r="R39" s="22" t="n">
+        <v>31.12752305309202</v>
+      </c>
+      <c r="S39" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>APPS</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Digital Turbine, Inc.</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>505977696</v>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>0.160493</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>0.2139901187024506</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>7.860368324264887</v>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>2.60006421311189</v>
+      </c>
+      <c r="N40" s="22" t="n">
+        <v>2.21076938537622</v>
+      </c>
+      <c r="O40" s="22" t="n">
+        <v>6.604902940406079</v>
+      </c>
+      <c r="P40" s="14" t="n">
+        <v>4.144803594723873</v>
+      </c>
+      <c r="Q40" s="22" t="n">
+        <v>14.00543319787248</v>
+      </c>
+      <c r="R40" s="22" t="n">
+        <v>-5.38117143279301</v>
+      </c>
+      <c r="S40" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>AMETEK, Inc.</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>51460661248</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="n">
+        <v>0.159807</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>0.213075801018176</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>22.33400482836672</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>34.74963248515428</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>4.712818164759142</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>3.05015318873502</v>
+      </c>
+      <c r="O41" s="22" t="n">
+        <v>16.30522088353413</v>
+      </c>
+      <c r="P41" s="14" t="n">
+        <v>0.7181031701883926</v>
+      </c>
+      <c r="Q41" s="22" t="n">
+        <v>31.09139197181419</v>
+      </c>
+      <c r="R41" s="22" t="n">
+        <v>26.5735453194523</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>AGCO</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>AGCO Corporation</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>8170577920</v>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>0.158309</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>0.2110790997975347</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>13.94065731027583</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>11.41461011455714</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>1.901682280926336</v>
+      </c>
+      <c r="N42" s="22" t="n">
+        <v>-22.7988768755295</v>
+      </c>
+      <c r="O42" s="22" t="n">
+        <v>7.57967416074283</v>
+      </c>
+      <c r="P42" s="14" t="n">
+        <v>1.876355353075171</v>
+      </c>
+      <c r="Q42" s="22" t="n">
+        <v>10.57892504626773</v>
+      </c>
+      <c r="R42" s="22" t="n">
+        <v>11.0526745752714</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -60457,7 +63035,1978 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:S35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Concentrated Segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MATCHES</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>TOP SCORER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>ACFN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>0.1% of universe</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>high conviction</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>risk-flagged</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>no thesis</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>by entry today asymmetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TOP NAMES MATCHING CONCENTRATED SEGMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Mcap (USD)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>FCF yld %</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>ROIC %</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA m %</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Mom 12m %</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>Arch #</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>ACFN</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Acorn Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>41637084</v>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0.292591</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0.3704147800002088</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>21.93666901408451</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>115.6585666666667</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>5.046919272727273</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>0.39628135342042</v>
+      </c>
+      <c r="O13" s="22" t="n">
+        <v>38.34586466165413</v>
+      </c>
+      <c r="P13" s="14" t="n">
+        <v>-1.621673003802281</v>
+      </c>
+      <c r="Q13" s="22" t="n">
+        <v>18.33071963756752</v>
+      </c>
+      <c r="R13" s="22" t="n">
+        <v>-6.584130816849671</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Array Digital Infrastructure Inc. Common Shares</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>4380064256</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.286534</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0.3926209975211729</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>18.53973660658124</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>14.76031439682422</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>2.356270549686185</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>7.3004408454048</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>11.42943288279336</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>0.5238097608260405</v>
+      </c>
+      <c r="Q14" s="22" t="n">
+        <v>74.7253268368884</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <v>43.79928174170437</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>AIFC</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Ai Financial Corporation</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>140535696</v>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0.251413</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>0.2672612419124244</v>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0.1579510644658788</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>-11.25265711851599</v>
+      </c>
+      <c r="O15" s="22" t="n">
+        <v>-2.67794085034032</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>0.5109806798728296</v>
+      </c>
+      <c r="Q15" s="22" t="n">
+        <v>-84.55684685057281</v>
+      </c>
+      <c r="R15" s="22" t="n">
+        <v>-83.92000007629395</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>ALTI</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Alvarium Tiedemann Holdings Inc. Class A Common St</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>527630080</v>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.251128</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0.3186098881680676</v>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>0.8792281363625759</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>-33.34495258496255</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>-13.93776260504201</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>-0.2202167179476625</v>
+      </c>
+      <c r="Q16" s="22" t="n">
+        <v>-37.87351461320508</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>-0.2865326772473</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>ALRM</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Alarm.Com Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>2166373632</v>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0.237296</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0.2932118040142897</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>10.99622089803185</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>18.45245549091591</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>2.519589901048136</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>5.00989295645193</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>27.5917038379382</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>-2.394972060132529</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>15.94287307964833</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>-23.07692256157664</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>ADTN</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Adtran Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1207681536</v>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0.227026</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.3671204310526602</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>33.56439486457765</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>8.781541799672787</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>7.33521192129909</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>-13.91397084962673</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>-1.122152971249677</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>3.22877997798453</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>82.05128951562541</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>AMCX</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Amc Global Media Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>364600032</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0.2596434397260048</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>5.110140868666113</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>3.023819267515924</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0.3816850167183466</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>43.64563522583564</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>10.00957540667602</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>3.917148204621456</v>
+      </c>
+      <c r="Q19" s="22" t="n">
+        <v>13.52815802578432</v>
+      </c>
+      <c r="R19" s="22" t="n">
+        <v>29.28349053114311</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>ABG</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Asbury Automotive Group Inc</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>3495121152</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0.208513</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.2700247489024741</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>5.643655862205504</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>5.45686362529274</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0.8888914425228891</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>18.73182563715605</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>15.12169691440487</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>4.662273178658482</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>6.16642729104735</v>
+      </c>
+      <c r="R20" s="22" t="n">
+        <v>-17.1616430364512</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ADMA</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>ADMA Biologics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>1909807104</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0.205523</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0.265293577739743</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>10.1155120346961</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>12.71560184827623</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>4.892863905719593</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>0.52875130576538</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>41.63688070248109</v>
+      </c>
+      <c r="P21" s="14" t="n">
+        <v>0.2650235854379669</v>
+      </c>
+      <c r="Q21" s="22" t="n">
+        <v>43.44982191329451</v>
+      </c>
+      <c r="R21" s="22" t="n">
+        <v>-59.12698495294922</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>ALL-PH</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>The Allstate Corporation</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>30043043840</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.200939</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.2644285487094155</v>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>2.70926538371359</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>0.9505186775081468</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>25.10065238449553</v>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="n">
+        <v>4.22314981985413</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>ALCO</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Alico, Inc.</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>297913856</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.170595</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.2281448143342178</v>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>19.11296952588696</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>2.990622550594282</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>-15.55718173779738</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>-151.2777345784797</v>
+      </c>
+      <c r="P23" s="14" t="n">
+        <v>10.25151515151515</v>
+      </c>
+      <c r="Q23" s="22" t="n">
+        <v>17.03430950824185</v>
+      </c>
+      <c r="R23" s="22" t="n">
+        <v>30.95054611412791</v>
+      </c>
+      <c r="S23" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Antero Midstream Corporation</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>10530307072</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0.163557</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.2180760998411859</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>16.35544022405969</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>22.48989174412247</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>5.437947021584353</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>7.22537334189526</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>13.07962357466979</v>
+      </c>
+      <c r="P24" s="14" t="n">
+        <v>3.78047792002079</v>
+      </c>
+      <c r="Q24" s="22" t="n">
+        <v>75.42081414178182</v>
+      </c>
+      <c r="R24" s="22" t="n">
+        <v>25.73044160199031</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>AMC</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>AMC Entertainment Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>965339776</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0.154506</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.2060076338589418</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>18.67388029292108</v>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>-111.3804721126502</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>-3.72158756330232</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>11.26732981038234</v>
+      </c>
+      <c r="Q25" s="22" t="n">
+        <v>6.393338367979649</v>
+      </c>
+      <c r="R25" s="22" t="n">
+        <v>-54.44839866709587</v>
+      </c>
+      <c r="S25" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>AGX</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Argan Inc</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>9162950656</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>0.152177</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.361068373539376</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>65.53148298671826</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>62.18493828299966</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>19.35108298645649</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>1.76056824986136</v>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>112.545043513734</v>
+      </c>
+      <c r="P26" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>13.80519974114287</v>
+      </c>
+      <c r="R26" s="22" t="n">
+        <v>235.1505228371443</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>9258790912</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0.151987</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>0.2026494686887169</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>8.282046370007665</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>17.2038925861236</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>4.077699081120694</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>3.49114698746531</v>
+      </c>
+      <c r="O27" s="22" t="n">
+        <v>43.12262212142653</v>
+      </c>
+      <c r="P27" s="14" t="n">
+        <v>1.299750396569807</v>
+      </c>
+      <c r="Q27" s="22" t="n">
+        <v>8.10000904550866</v>
+      </c>
+      <c r="R27" s="22" t="n">
+        <v>-32.15955219569812</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>ACDC</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>ProFrac Holding Corp. Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1317103104</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>0.147744</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0.1969925727619505</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>9.163876042236996</v>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>1.835683768641115</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>9.437378108251721</v>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>-9.949491876102961</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>5.264705882352941</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>9.80533525594808</v>
+      </c>
+      <c r="R28" s="22" t="n">
+        <v>15.92356634699089</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Applied Materials, Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>343117496320</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>0.139447</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>0.2877785867906208</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>37.20696903533492</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>39.2223932693187</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>15.79948871022701</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>1.65045503675468</v>
+      </c>
+      <c r="O29" s="22" t="n">
+        <v>36.38781531812326</v>
+      </c>
+      <c r="P29" s="14" t="n">
+        <v>-0.1324310776942356</v>
+      </c>
+      <c r="Q29" s="22" t="n">
+        <v>35.16285956006768</v>
+      </c>
+      <c r="R29" s="22" t="n">
+        <v>171.1999831469766</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>AJG</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Arthur J. Gallagher &amp; Co.</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>52608876544</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>0.129572</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>0.1727624006985841</v>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>24.00806669283073</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>2.212781347802313</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>6.40234162229822</v>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P30" s="14" t="n">
+        <v>2.94790996784566</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>25.96409441246009</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>-38.36357623194796</v>
+      </c>
+      <c r="S30" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>AIV</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Apartment Investment and Management Company</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>602757376</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>0.129054</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>0.1720725503865425</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>8.028123669567698</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>0.6967608685851679</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>1.665752048483777</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>-22.72008696248621</v>
+      </c>
+      <c r="O31" s="22" t="n">
+        <v>8.680668700812671</v>
+      </c>
+      <c r="P31" s="14" t="n">
+        <v>2.721352228643813</v>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>72.22625671170681</v>
+      </c>
+      <c r="R31" s="22" t="n">
+        <v>-4.60341727126382</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>ALK</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Alaska Air Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>4606473728</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>0.127827</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>0.1704356718375114</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>12.32907039786382</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>20.56461485714286</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>1.234648546770303</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>19.49430416896974</v>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>-0.61012082785022</v>
+      </c>
+      <c r="P32" s="14" t="n">
+        <v>4.370736086175943</v>
+      </c>
+      <c r="Q32" s="22" t="n">
+        <v>7.735036800444379</v>
+      </c>
+      <c r="R32" s="22" t="n">
+        <v>-17.50149740758932</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>AGNT</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>eXp World Holdings Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>780538624</v>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>0.119153</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>0.1441307192961611</v>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>3.215017048426759</v>
+      </c>
+      <c r="N33" s="22" t="n">
+        <v>21.70104012687526</v>
+      </c>
+      <c r="O33" s="22" t="n">
+        <v>-13.01187285134061</v>
+      </c>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q33" s="22" t="n">
+        <v>-0.24943889868032</v>
+      </c>
+      <c r="R33" s="22" t="n">
+        <v>-38.36826117700587</v>
+      </c>
+      <c r="S33" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ANAB</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>AnaptysBio, Inc.</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>1837721984</v>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>0.114531</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>0.3621653322381127</v>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>49.38785229776942</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>-5.37045324914609</v>
+      </c>
+      <c r="O34" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P34" s="14" t="n">
+        <v>-4.296528419593345</v>
+      </c>
+      <c r="Q34" s="22" t="n">
+        <v>29.51709909932951</v>
+      </c>
+      <c r="R34" s="22" t="n">
+        <v>364.3382334894788</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>AMRZ</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Amrize Ltd Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>27649155072</v>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>0.09833799999999999</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>0.1311167867040548</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>14.38478981555154</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>32.37605980327869</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>2.11158966488468</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <v>-12.14503658884177</v>
+      </c>
+      <c r="O35" s="22" t="n">
+        <v>7.848702502316959</v>
+      </c>
+      <c r="P35" s="14" t="n">
+        <v>1.78721098265896</v>
+      </c>
+      <c r="Q35" s="22" t="n">
+        <v>23.23707186030893</v>
+      </c>
+      <c r="R35" s="22" t="n">
+        <v>-2.96960978483845</v>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62176,6 +66725,3044 @@
       </c>
       <c r="S32" s="16" t="n">
         <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:S32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Diversified Segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MATCHES</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>TOP SCORER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>ACTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>0.1% of universe</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>high conviction</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>risk-flagged</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>no thesis</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>by entry today asymmetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TOP NAMES MATCHING DIVERSIFIED SEGMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Mcap (USD)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>FCF yld %</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>ROIC %</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA m %</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Mom 12m %</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>Arch #</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>ACTG</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Acacia Research Corporation</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>442378240</v>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0.5964970000000001</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0.6554225327075763</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>5.916304114396459</v>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.8140182905511086</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>12.17080659301868</v>
+      </c>
+      <c r="O13" s="22" t="n">
+        <v>3.56924240530466</v>
+      </c>
+      <c r="P13" s="14" t="n">
+        <v>-3.064616009946442</v>
+      </c>
+      <c r="Q13" s="22" t="n">
+        <v>29.32630279912492</v>
+      </c>
+      <c r="R13" s="22" t="n">
+        <v>23.45013144510961</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Adobe Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>98931990528</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.218527</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0.2913698523763092</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>10.21890603178509</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>14.0050949218573</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>8.65319605772763</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>8.193507435500159</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>72.95730960737899</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>-0.0233696194946569</v>
+      </c>
+      <c r="Q14" s="22" t="n">
+        <v>40.94794094794095</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <v>-40.92631418456457</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>APEI</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>American Public Education, Inc.</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>978074752</v>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0.200725</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>0.3216859979697861</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>12.65653683879564</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>30.29689780999288</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>3.317959549768982</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>12.04509162097254</v>
+      </c>
+      <c r="O15" s="22" t="n">
+        <v>29.18187426844948</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>-0.173664181665055</v>
+      </c>
+      <c r="Q15" s="22" t="n">
+        <v>9.881608107733229</v>
+      </c>
+      <c r="R15" s="22" t="n">
+        <v>91.7985653170185</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>APOG</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Apogee Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>726147584</v>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.198035</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0.264047269094791</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>6.833419477660777</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>13.4146345716872</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>1.418827856520397</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>13.10436088981052</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>11.98978071109218</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>1.362917082069449</v>
+      </c>
+      <c r="Q16" s="22" t="n">
+        <v>10.06803428124775</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>-14.64558526899825</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>ALGN</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Align Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>11717441536</v>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0.2375562152103406</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>14.71283180120794</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>30.2493314677227</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>2.823875230725073</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>2.58345645736704</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>17.23163466938116</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>-1.075598092667894</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>21.42336922141252</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>-5.21406637400838</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Analog Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>193407647744</v>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0.183277</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.3112991279776929</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>46.8849507718971</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>62.48098758182941</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>5.731950050075524</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>2.26621545276302</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>9.819221046127851</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>1.003346988184371</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>48.87752485382285</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>90.21757087039752</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>AHCO</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>AdaptHealth Corp.</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1450337152</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0.17974</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0.2368121471363271</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>5.785815773708095</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>74.96832172025225</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0.9550727280150564</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>-1.05327233594854</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>5.168220566313471</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>3.449884239174141</v>
+      </c>
+      <c r="Q19" s="22" t="n">
+        <v>14.56230582734462</v>
+      </c>
+      <c r="R19" s="22" t="n">
+        <v>17.92035279198179</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>4535749181440</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0.164026</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.2392797053557943</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>29.20370391631436</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>37.83290528271985</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>42.59279358293189</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>3.22478148920843</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>100.6231158577764</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>0.2446554483172476</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>35.43666739027383</v>
+      </c>
+      <c r="R20" s="22" t="n">
+        <v>53.97554948831738</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ANGO</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>AngioDynamics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>445004736</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0.161819</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0.2007181009440836</v>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>2.566984523267016</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>-19.82765414883135</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>-29.29316030601931</v>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="n">
+        <v>0.87369511514861</v>
+      </c>
+      <c r="R21" s="22" t="n">
+        <v>17.44820466911453</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Aes Corp</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>10469154816</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.154903</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.2182178902359923</v>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>5.458370602711158</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>2.368587062443439</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>-47.72113974630138</v>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="n">
+        <v>60.27743347793927</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>ABM</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>ABM Industries Incorporated</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>2352433920</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.147622</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.1968296297641992</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>9.765376850790741</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>14.17983074141049</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>1.364204314544189</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>-7.332830841004021</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>8.950938029863801</v>
+      </c>
+      <c r="P23" s="14" t="n">
+        <v>3.646722288438617</v>
+      </c>
+      <c r="Q23" s="22" t="n">
+        <v>4.7269736100782</v>
+      </c>
+      <c r="R23" s="22" t="n">
+        <v>-19.72958822237768</v>
+      </c>
+      <c r="S23" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>AORT</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Artivion Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>1105332096</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0.141515</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.1886865728732084</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>24.19464233660412</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>69.82514819962097</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>2.465982116404005</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>-4.06538452675131</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>4.7294096433928</v>
+      </c>
+      <c r="P24" s="14" t="n">
+        <v>2.353588216859919</v>
+      </c>
+      <c r="Q24" s="22" t="n">
+        <v>14.46083429633154</v>
+      </c>
+      <c r="R24" s="22" t="n">
+        <v>-21.40144633256089</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>AEE</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Ameren Corporation</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>30799687680</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0.14065</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.1875336270598693</v>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>15.430705250501</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>2.272033614635585</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>-9.259834156863759</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>6.52826041759482</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>5.10453128746104</v>
+      </c>
+      <c r="Q25" s="22" t="n">
+        <v>46.98130209506645</v>
+      </c>
+      <c r="R25" s="22" t="n">
+        <v>20.02858402752058</v>
+      </c>
+      <c r="S25" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>AutoNation, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>6357015040</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>0.123252</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.1643359452354363</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>5.873982511515518</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>10.71467224001348</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>2.854647734518838</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>7.135424364199711</v>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>33.99199736899803</v>
+      </c>
+      <c r="P26" s="14" t="n">
+        <v>6.111654641066406</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>5.94840159894664</v>
+      </c>
+      <c r="R26" s="22" t="n">
+        <v>5.19962322391291</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>152251891712</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0.119211</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>0.1589484771554739</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>20.89104884916201</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>28.08557308836008</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>2.924490342329191</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>2.12739557031376</v>
+      </c>
+      <c r="O27" s="22" t="n">
+        <v>9.012042115881719</v>
+      </c>
+      <c r="P27" s="14" t="n">
+        <v>2.301791145657317</v>
+      </c>
+      <c r="Q27" s="22" t="n">
+        <v>26.22413258297514</v>
+      </c>
+      <c r="R27" s="22" t="n">
+        <v>-32.17061762665802</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Allison Transmission Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>9112176640</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>0.112485</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>0.1499805711958595</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>12.45532122137405</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>14.32732176100629</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>4.788321933788755</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>6.463878206821059</v>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>15.46885694729637</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>3.920713577799802</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>27.64383561643835</v>
+      </c>
+      <c r="R28" s="22" t="n">
+        <v>7.33775642185242</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>AMT</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>American Tower Corporation</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>85654437888</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>0.105467</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>0.1406222415565577</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>21.42430454791428</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>24.44545731556266</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>24.31568667688639</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>3.98169678547129</v>
+      </c>
+      <c r="O29" s="22" t="n">
+        <v>10.49183331699854</v>
+      </c>
+      <c r="P29" s="14" t="n">
+        <v>5.180633930514253</v>
+      </c>
+      <c r="Q29" s="22" t="n">
+        <v>63.71484291959738</v>
+      </c>
+      <c r="R29" s="22" t="n">
+        <v>-9.33789724133883</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>APD</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Air Products and Chemicals, Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>64459378688</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>0.104024</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>0.1386987814866156</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>49.47671479234168</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>22.98180928693668</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>4.11883645825213</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>-4.01834465786155</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>-0.27312444572603</v>
+      </c>
+      <c r="P30" s="14" t="n">
+        <v>3.702672335925624</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>36.41797511212381</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>10.39814011953049</v>
+      </c>
+      <c r="S30" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Alto Ingredients, Inc.</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>361859840</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>0.099179</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>0.3253062964331374</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>15.59687633377943</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>9.96118149035153</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>1.475527501518914</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>-29.57609222399479</v>
+      </c>
+      <c r="O31" s="22" t="n">
+        <v>0.75025452267209</v>
+      </c>
+      <c r="P31" s="14" t="n">
+        <v>1.154297917778965</v>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>5.30521490271012</v>
+      </c>
+      <c r="R31" s="22" t="n">
+        <v>436.781615022782</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>AIN</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Albany International Corp.</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>1719728640</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>0.09281</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>0.1237465338725046</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>55.75245705067886</v>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>2.357727285813976</v>
+      </c>
+      <c r="N32" s="22" t="n">
+        <v>-4.51582872981635</v>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>-3.74760588341171</v>
+      </c>
+      <c r="P32" s="14" t="n">
+        <v>6.410314916426722</v>
+      </c>
+      <c r="Q32" s="22" t="n">
+        <v>4.581241309736741</v>
+      </c>
+      <c r="R32" s="22" t="n">
+        <v>-9.642924650919179</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:S26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Fastest Segment Inflection</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MATCHES</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>TOP SCORER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>AAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>0.1% of universe</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>high conviction</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>risk-flagged</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>no thesis</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>by entry today asymmetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TOP NAMES MATCHING FASTEST SEGMENT INFLECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Mcap (USD)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Asym</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>FCF yld %</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>ROIC %</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA m %</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Mom 12m %</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>Arch #</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>AAME</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Atlantic American Corporation</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>45893764</v>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0.6477579999999999</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0.6139274688603981</v>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>6.049797521750593</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.4191670685371912</v>
+      </c>
+      <c r="N13" s="22" t="n">
+        <v>-56.69833487617185</v>
+      </c>
+      <c r="O13" s="22" t="n">
+        <v>-6.60679068279942</v>
+      </c>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R13" s="22" t="n">
+        <v>26.4044964137425</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Adobe Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>98931990528</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.218527</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0.2913698523763092</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>10.21890603178509</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>14.0050949218573</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>8.65319605772763</v>
+      </c>
+      <c r="N14" s="22" t="n">
+        <v>8.193507435500159</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>72.95730960737899</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>-0.0233696194946569</v>
+      </c>
+      <c r="Q14" s="22" t="n">
+        <v>40.94794094794095</v>
+      </c>
+      <c r="R14" s="22" t="n">
+        <v>-40.92631418456457</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>AMTM</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Amentum Holdings Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>5675467776</v>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0.206685</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>0.275580506419152</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>16.98975514074074</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>53.04175491588785</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>1.231388105011933</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <v>6.09641378747914</v>
+      </c>
+      <c r="O15" s="22" t="n">
+        <v>6.19141588554514</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>3.563136456211812</v>
+      </c>
+      <c r="Q15" s="22" t="n">
+        <v>6.91500598549398</v>
+      </c>
+      <c r="R15" s="22" t="n">
+        <v>9.5238120931484</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Analog Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>193407647744</v>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.183277</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0.3112991279776929</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>46.8849507718971</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>62.48098758182941</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>5.731950050075524</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>2.26621545276302</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>9.819221046127851</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>1.003346988184371</v>
+      </c>
+      <c r="Q16" s="22" t="n">
+        <v>48.87752485382285</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>90.21757087039752</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Agilent Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>32487960576</v>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0.176896</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0.2358608671721763</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>20.25950034285714</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>27.18657788786611</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>4.702947390851187</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>3.45974317892499</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>16.28604382929642</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>25.81740976645435</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>5.67433603220212</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>ALCO</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Alico, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>297913856</v>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0.170595</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0.2281448143342178</v>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>19.11296952588696</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>2.990622550594282</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <v>-15.55718173779738</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>-151.2777345784797</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>10.25151515151515</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>17.03430950824185</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>30.95054611412791</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>4535749181440</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0.164026</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0.2392797053557943</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>29.20370391631436</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>37.83290528271985</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>42.59279358293189</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>3.22478148920843</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>100.6231158577764</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>0.2446554483172476</v>
+      </c>
+      <c r="Q19" s="22" t="n">
+        <v>35.43666739027383</v>
+      </c>
+      <c r="R19" s="22" t="n">
+        <v>53.97554948831738</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>AIT</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Applied Industrial Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>11350275072</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0.162274</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.220702878537568</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>21.15754172218445</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>28.68230148285168</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>6.102157354426753</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>2.76077009598662</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>25.29819594919969</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>0.3163579415275729</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>12.65532746305899</v>
+      </c>
+      <c r="R20" s="22" t="n">
+        <v>38.52677284564677</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ANGO</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>AngioDynamics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>445004736</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0.161819</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0.2007181009440836</v>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>2.566984523267016</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>-19.82765414883135</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>-29.29316030601931</v>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="n">
+        <v>0.87369511514861</v>
+      </c>
+      <c r="R21" s="22" t="n">
+        <v>17.44820466911453</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>ALGT</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Allegiant Travel Company</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2012932096</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.161064</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0.2191350810952704</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>11.73241162672922</v>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>1.836494554651013</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>17.55036847502281</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>1.97457438394139</v>
+      </c>
+      <c r="P22" s="14" t="n">
+        <v>4.485509099559891</v>
+      </c>
+      <c r="Q22" s="22" t="n">
+        <v>12.73818276724027</v>
+      </c>
+      <c r="R22" s="22" t="n">
+        <v>35.54108541601705</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>9258790912</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.151987</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0.2026494686887169</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>8.282046370007665</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>17.2038925861236</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>4.077699081120694</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>3.49114698746531</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>43.12262212142653</v>
+      </c>
+      <c r="P23" s="14" t="n">
+        <v>1.299750396569807</v>
+      </c>
+      <c r="Q23" s="22" t="n">
+        <v>8.10000904550866</v>
+      </c>
+      <c r="R23" s="22" t="n">
+        <v>-32.15955219569812</v>
+      </c>
+      <c r="S23" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>ABM</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>ABM Industries Incorporated</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>2352433920</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0.147622</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0.1968296297641992</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>9.765376850790741</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>14.17983074141049</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>1.364204314544189</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>-7.332830841004021</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>8.950938029863801</v>
+      </c>
+      <c r="P24" s="14" t="n">
+        <v>3.646722288438617</v>
+      </c>
+      <c r="Q24" s="22" t="n">
+        <v>4.7269736100782</v>
+      </c>
+      <c r="R24" s="22" t="n">
+        <v>-19.72958822237768</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Applied Materials, Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>Mega Cap</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>343117496320</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0.139447</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0.2877785867906208</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>37.20696903533492</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>39.2223932693187</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>15.79948871022701</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>1.65045503675468</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>36.38781531812326</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>-0.1324310776942356</v>
+      </c>
+      <c r="Q25" s="22" t="n">
+        <v>35.16285956006768</v>
+      </c>
+      <c r="R25" s="22" t="n">
+        <v>171.1999831469766</v>
+      </c>
+      <c r="S25" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>APD</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Air Products and Chemicals, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>64459378688</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>0.104024</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>0.1386987814866156</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>49.47671479234168</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>22.98180928693668</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>4.11883645825213</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>-4.01834465786155</v>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>-0.27312444572603</v>
+      </c>
+      <c r="P26" s="14" t="n">
+        <v>3.702672335925624</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>36.41797511212381</v>
+      </c>
+      <c r="R26" s="22" t="n">
+        <v>10.39814011953049</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/top_by_archetype_book.xlsx
+++ b/top_by_archetype_book.xlsx
@@ -44,7 +44,43 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Double Inflection" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiet Compounder" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Density'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Narrative Lag'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KPI Threshold'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Capital Discipline'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fixed-Cost + Demand Shock'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Low-SBC Quality'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Lindy FCF'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Lindy Margin'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'No Dilution'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Strong Coverage'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Global Geographic Footprint'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Capital Returner'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Discounted Vehicle'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cash Reinvestment'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Regime-Change Cyclical'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Cheap per ROIIC'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Tax Efficient'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Concentrated Segments'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Durable Reinvestment'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Blind-Spot Geography'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Cash Quality'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Fastest Segment Inflection'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Diversified Segments'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Capital-Light Pivot'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Dead Option'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Lindy Growth'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'ROIC Inflection'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Buyback Compounder'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'QARP'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Microcap Activist Inflect'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Owner-Operator'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'Tangible Value'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'Reinvestment Inflection'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'Double Inflection'!$A$11:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'Quiet Compounder'!$A$11:$S$42</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -4160,6 +4196,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -6594,6 +6631,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -9052,6 +9090,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -11560,6 +11599,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -14002,6 +14042,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -16504,6 +16545,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -18948,6 +18990,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -21384,6 +21427,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -23864,6 +23908,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -26338,6 +26383,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -28774,6 +28820,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -31210,6 +31257,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -33656,6 +33704,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -36092,6 +36141,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -38554,6 +38604,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -41000,6 +41051,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -43432,6 +43484,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -45876,6 +45929,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -48346,6 +48400,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -50814,6 +50869,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -53238,6 +53294,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -55690,6 +55747,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -58120,6 +58178,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -60554,6 +60613,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -62988,6 +63048,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -65490,6 +65551,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -67938,6 +68000,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -70412,6 +70475,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -72896,6 +72960,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -75334,6 +75399,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -77774,6 +77840,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -80212,6 +80279,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -82656,6 +82724,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -85086,6 +85155,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
@@ -87516,6 +87586,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:S42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A10:S10"/>
